--- a/ValueSet-dk-core-priority-codes.xlsx
+++ b/ValueSet-dk-core-priority-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-priority-codes.xlsx
+++ b/ValueSet-dk-core-priority-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-priority-codes.xlsx
+++ b/ValueSet-dk-core-priority-codes.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-priority-codes.xlsx
+++ b/ValueSet-dk-core-priority-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-dk-core-priority-codes.xlsx
+++ b/ValueSet-dk-core-priority-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
